--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-med-req.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
